--- a/Field-trails/2025-10-14-inital-lab-acidification/2025-10-14-titration-pig-2nd.xlsx
+++ b/Field-trails/2025-10-14-inital-lab-acidification/2025-10-14-titration-pig-2nd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au705323_uni_au_dk/Documents/10 semester - Speciale/Fall Experiments/slurry acidification - initial lab scale/2nd trial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-14-inital-lab-acidification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="981" documentId="11_AD4D1D646341095ACB70003C5D95D01A683EDF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C46E1ED-7AA2-4750-8932-892E5EC9B20D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EDC234-CA16-4D7B-8FAE-3D343BDEA0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>Triplicates of cattle and pig slurry with acetic acid and H2SO4 (12 in total)</t>
-  </si>
-  <si>
-    <t>2 setups - pH meters and pipettes switched to reduce systematic errors</t>
   </si>
   <si>
     <t>Encountered issues with foam formation in cattle slurry, one sample was stopped prematurely</t>
@@ -379,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -389,8 +386,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -749,14 +745,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -784,37 +775,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
-      </c>
-      <c r="K1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1010,7 +1001,7 @@
         <f>'Raw Data'!B8</f>
         <v>1.6</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="9">
         <f>'Raw Data'!C8</f>
         <v>3.0133920000000001</v>
       </c>
@@ -1030,7 +1021,7 @@
         <f>'Raw Data'!W8</f>
         <v>2.9439202887759666E-2</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="7">
         <f>'Raw Data'!AE8</f>
         <v>5.833333333333333</v>
       </c>
@@ -1236,7 +1227,7 @@
         <f>'Raw Data'!A13</f>
         <v>0.9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <f>'Raw Data'!B13</f>
         <v>3.6</v>
       </c>
@@ -1268,7 +1259,7 @@
         <f>'Raw Data'!AF13</f>
         <v>2.1602468994692817E-2</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="7">
         <f>'Raw Data'!AN13</f>
         <v>5.8</v>
       </c>
@@ -2007,195 +1998,195 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="E3">
         <f>250*10^-6</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
         <v>35</v>
       </c>
-      <c r="J3" t="s">
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="s">
         <v>36</v>
       </c>
-      <c r="K3" t="s">
+      <c r="AC3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK3" t="s">
         <v>35</v>
       </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="AL3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>36</v>
-      </c>
       <c r="AN3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AO3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.3">
@@ -2211,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5">
         <v>1.88337</v>
@@ -2502,7 +2493,7 @@
       <c r="AC7" s="3">
         <v>5.95</v>
       </c>
-      <c r="AE7" s="9">
+      <c r="AE7" s="3">
         <f t="shared" si="6"/>
         <v>5.97</v>
       </c>
@@ -2566,7 +2557,7 @@
       <c r="T8">
         <v>6.69</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8">
         <f t="shared" si="4"/>
         <v>6.6499999999999995</v>
       </c>
